--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T2_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T2_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>81</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.61e+05</t>
-  </si>
-  <si>
-    <t>(65822.607)</t>
-  </si>
-  <si>
-    <t>494.233</t>
-  </si>
-  <si>
-    <t>(33.939)</t>
-  </si>
-  <si>
-    <t>3.583</t>
-  </si>
-  <si>
-    <t>(0.045)</t>
-  </si>
-  <si>
-    <t>11.634</t>
-  </si>
-  <si>
-    <t>(1.815)</t>
-  </si>
-  <si>
-    <t>88.750</t>
-  </si>
-  <si>
-    <t>(0.454)</t>
-  </si>
-  <si>
-    <t>1.08e+06</t>
-  </si>
-  <si>
-    <t>(53579.033)</t>
-  </si>
-  <si>
-    <t>2.583</t>
-  </si>
-  <si>
-    <t>(0.121)</t>
-  </si>
-  <si>
-    <t>3.537</t>
-  </si>
-  <si>
-    <t>(0.428)</t>
-  </si>
-  <si>
-    <t>33.878</t>
-  </si>
-  <si>
-    <t>(3.332)</t>
-  </si>
-  <si>
-    <t>0.976</t>
-  </si>
-  <si>
-    <t>(0.017)</t>
-  </si>
-  <si>
-    <t>32</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>7.86e+05</t>
-  </si>
-  <si>
-    <t>(1.62e+05)</t>
-  </si>
-  <si>
-    <t>499.679</t>
-  </si>
-  <si>
-    <t>(60.412)</t>
-  </si>
-  <si>
-    <t>3.317</t>
-  </si>
-  <si>
-    <t>(0.064)</t>
-  </si>
-  <si>
-    <t>28.281</t>
-  </si>
-  <si>
-    <t>(4.792)</t>
-  </si>
-  <si>
-    <t>91.235</t>
-  </si>
-  <si>
-    <t>(0.529)</t>
-  </si>
-  <si>
-    <t>1.36e+06</t>
-  </si>
-  <si>
-    <t>(79662.261)</t>
-  </si>
-  <si>
-    <t>3.392</t>
-  </si>
-  <si>
-    <t>(0.173)</t>
-  </si>
-  <si>
-    <t>6.406</t>
-  </si>
-  <si>
-    <t>(0.717)</t>
-  </si>
-  <si>
-    <t>47.312</t>
-  </si>
-  <si>
-    <t>(3.806)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -201,10 +201,10 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>113</t>
+    <t>116</t>
+  </si>
+  <si>
+    <t>115</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>2.25e+05</t>
-  </si>
-  <si>
-    <t>5.447</t>
-  </si>
-  <si>
-    <t>-0.265***</t>
-  </si>
-  <si>
-    <t>16.647***</t>
-  </si>
-  <si>
-    <t>2.486***</t>
-  </si>
-  <si>
-    <t>2.86e+05***</t>
-  </si>
-  <si>
-    <t>0.809***</t>
-  </si>
-  <si>
-    <t>2.870***</t>
-  </si>
-  <si>
-    <t>13.434**</t>
-  </si>
-  <si>
-    <t>0.024</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T2_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T2_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>82</t>
+  </si>
+  <si>
+    <t>81</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.61e+05</t>
+  </si>
+  <si>
+    <t>(65822.607)</t>
+  </si>
+  <si>
+    <t>494.233</t>
+  </si>
+  <si>
+    <t>(33.939)</t>
+  </si>
+  <si>
+    <t>3.583</t>
+  </si>
+  <si>
+    <t>(0.045)</t>
+  </si>
+  <si>
+    <t>11.634</t>
+  </si>
+  <si>
+    <t>(1.815)</t>
+  </si>
+  <si>
+    <t>88.750</t>
+  </si>
+  <si>
+    <t>(0.454)</t>
+  </si>
+  <si>
+    <t>1.08e+06</t>
+  </si>
+  <si>
+    <t>(53579.033)</t>
+  </si>
+  <si>
+    <t>2.583</t>
+  </si>
+  <si>
+    <t>(0.121)</t>
+  </si>
+  <si>
+    <t>3.537</t>
+  </si>
+  <si>
+    <t>(0.428)</t>
+  </si>
+  <si>
+    <t>33.878</t>
+  </si>
+  <si>
+    <t>(3.332)</t>
+  </si>
+  <si>
+    <t>0.976</t>
+  </si>
+  <si>
+    <t>(0.017)</t>
+  </si>
+  <si>
+    <t>32</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>7.86e+05</t>
+  </si>
+  <si>
+    <t>(1.62e+05)</t>
+  </si>
+  <si>
+    <t>499.679</t>
+  </si>
+  <si>
+    <t>(60.412)</t>
+  </si>
+  <si>
+    <t>3.317</t>
+  </si>
+  <si>
+    <t>(0.064)</t>
+  </si>
+  <si>
+    <t>28.281</t>
+  </si>
+  <si>
+    <t>(4.792)</t>
+  </si>
+  <si>
+    <t>91.235</t>
+  </si>
+  <si>
+    <t>(0.529)</t>
+  </si>
+  <si>
+    <t>1.36e+06</t>
+  </si>
+  <si>
+    <t>(79662.261)</t>
+  </si>
+  <si>
+    <t>3.392</t>
+  </si>
+  <si>
+    <t>(0.173)</t>
+  </si>
+  <si>
+    <t>6.406</t>
+  </si>
+  <si>
+    <t>(0.717)</t>
+  </si>
+  <si>
+    <t>47.312</t>
+  </si>
+  <si>
+    <t>(3.806)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -201,10 +201,10 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>115</t>
+    <t>114</t>
+  </si>
+  <si>
+    <t>113</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>2.25e+05</t>
+  </si>
+  <si>
+    <t>5.447</t>
+  </si>
+  <si>
+    <t>-0.265***</t>
+  </si>
+  <si>
+    <t>16.647***</t>
+  </si>
+  <si>
+    <t>2.486***</t>
+  </si>
+  <si>
+    <t>2.86e+05***</t>
+  </si>
+  <si>
+    <t>0.809***</t>
+  </si>
+  <si>
+    <t>2.870***</t>
+  </si>
+  <si>
+    <t>13.434**</t>
+  </si>
+  <si>
+    <t>0.024</t>
   </si>
 </sst>
 </file>
